--- a/output/US_Alpha_Records.xlsx
+++ b/output/US_Alpha_Records.xlsx
@@ -19,8 +19,10 @@
     <sheet name="持倉管理" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="復盤紀錄" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="交易計畫" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="模型修正" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="環境記憶" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="時間閘門" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="出場計畫" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="模型修正" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="環境記憶" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推薦紀錄'!$A$1:$T$1</definedName>
@@ -29,13 +31,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'催化劑'!$A$1:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'資訊收錄'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'資訊收錄'!$A$1:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'排除名單'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$T$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'復盤紀錄'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'模型修正'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'時間閘門'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'出場計畫'!$A$1:$R$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'模型修正'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -512,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -530,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>匯出時間：2026-05-10 05:12</t>
+          <t>匯出時間：2026-05-10 05:26</t>
         </is>
       </c>
     </row>
@@ -664,44 +668,44 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>時間閘門</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>出場計畫</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>環境記憶</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>勝率統計</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>總推薦數</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>勝利</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>部分成功</t>
+          <t>總推薦數</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -711,7 +715,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>虧損</t>
+          <t>勝利</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -721,31 +725,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>勝率</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>部分成功</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>平均報酬</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>虧損</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>平均MFE</t>
+          <t>勝率</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -757,31 +757,55 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>平均報酬</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>平均MFE</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>平均MAE</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>系統版本</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>HIGH_ALPHA_LAUNCHPAD_US_v2.2</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>含：TIMING + EXIT + TRADE_PLAN</t>
         </is>
@@ -798,16 +822,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,22 +865,87 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>股數</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>現價</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>持倉金額</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>盈虧%</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>推薦ID</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>買入理由</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>警戒價</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>失效價</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>停損價</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>可否加碼</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>加碼條件</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>持有天數</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>邏輯有效</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>下一步</t>
         </is>
       </c>
     </row>
@@ -864,13 +966,28 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>165.5</v>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="T2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -891,9 +1008,22 @@
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="T3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -912,20 +1042,43 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>7.73</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>7.88</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
         <v>1.94</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="T4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:T4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1118,6 +1271,506 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>時間狀態</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>財報日期</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>距財報天數</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>催化劑日期</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>距事件天數</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>FOMC週</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>OPEX週</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>CPI/NFP</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>財報季</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>通過</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>動作</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>T3_earnings_zone</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>S3過熱+距財報遠，但市場進入財報季擁擠</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>T4_event_lockout</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>距財報4天，禁止追買，持有不加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>T0_clear</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>無事件衝突，可正常操作</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>推薦ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>進場價</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>停損</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>移動停損規則</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>T1出場比</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>T2出場比</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>剩餘部位</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>時間停損天數</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>利多出盡規則</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>結構失效規則</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>獲利鎖定規則</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>實際出場觸發</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>實際出場價</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>實際出場日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>事件後判斷</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>事件後確認方向再設</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>05-13事件後3天無正面反應=催化失效，快速退出</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>財報後跌破前低=結構失效</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>+5%保本，+10%停損上移至7.73+3%</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>跟蹤10EMA</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>若10天內無法突破8.20則減倉</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>跌破7.20+量增=波段失效</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>+5%-&gt;保本; +10%-&gt;+3%; +15%-&gt;10EMA</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1269,7 +1922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2279,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2289,8 +2942,11 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2326,15 +2982,30 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>進入評分</t>
+          <t>進入主分數</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>進入市場閘門</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>進入風險封鎖</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>進入板塊分數</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
           <t>結論</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>內容摘要</t>
         </is>
@@ -2374,12 +3045,15 @@
       <c r="G2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>市場極度追逐AI/半導體：MU/INTC/AMD/SOX過熱，散戶與媒體關注升高。啟動SENTIMENT_GAUGE雛形：過熱冷卻，不追高。</t>
         </is>
@@ -2419,12 +3093,15 @@
       <c r="G3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>消費可選股異常選擇權：TSLA/NKE/RCL/FLUT等出現bearish/neutral put或call flow；TPR/SGI有偏多流。選擇權流向歧義大，只能作情緒輔助，不可單獨做買賣依據。</t>
         </is>
@@ -2464,12 +3141,15 @@
       <c r="G4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>RPD先前持倉成本6.80、155股；後續因公司展望弱被降級。若仍持有需重新提供最新股數與成本；舊邏輯已削弱。</t>
         </is>
@@ -2509,12 +3189,15 @@
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>MRVL持倉盤中管理：仍有效但未breakout confirmed；167.4上方才可加碼。守165/164/162.8。後續已獲利+51.64美元稅費前。交易已關閉。</t>
         </is>
@@ -2554,12 +3237,15 @@
       <c r="G6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>CRSR進入S1-B/S2池。持倉120股，成本7.73；晚盤/收盤附近技術跟進至7.88。持有；8.20 T1，8.80-9.00 T2；7.20減倉/停損，7.00硬失效。</t>
         </is>
@@ -2599,12 +3285,15 @@
       <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>MIST IQVIA TRx：1月682、2月2947、3月9713、4月15876；但Q1 revenue $29.8M與TRx×ASP不一致。數據重要但未驗證；收入口徑有疑點；2026-05-13前不加碼。</t>
         </is>
@@ -2644,12 +3333,15 @@
       <c r="G8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>S1-A嚴格點火：GCTS、TRAW短線爆發動能強。需要SEC/流動性/催化劑檢查，未通過前不主推。</t>
         </is>
@@ -2689,12 +3381,15 @@
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>富途區間漲幅/選股器結果：GRPN、SHMD、FNKO、MX、GCTS、TRAW、EVTV等進入S1/S2池。大多是高波動小票，只能逐檔排雷，不能直接推薦。</t>
         </is>
@@ -2734,12 +3429,15 @@
       <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>富途熱力圖與板塊榜單：半導體、電腦硬體、半導體設備、太陽能強；軟體、醫療、廣告偏弱。板塊主線偏硬體，但多數已過熱。</t>
         </is>
@@ -2779,12 +3477,15 @@
       <c r="G11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Rapid7分析師與財報電話會議：RPD Q1略優但ARR近乎持平，FY2026營收預期下滑，多家券商降目標價。RPD從可交易候選降為C+/B-，只能hold-only/watch，不可加碼。</t>
         </is>
@@ -2824,12 +3525,15 @@
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>IBD盤中更新：軟體強，半導體分化，小型股弱。DDOG/FTNT/ZS強，ARM/SNDK弱，小型股IWM弱。軟體/網安升溫，但小型股不能激進。</t>
         </is>
@@ -2869,12 +3573,15 @@
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>AI生產力、Agentic AI、雲端/軟體牛市。AI推升生產力，agentic AI、雲端、軟體應用受益。支持AI software/cloud/cybersecurity輪動。</t>
         </is>
@@ -2914,12 +3621,15 @@
       <c r="G14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Intel類Cisco泡沫警告：INTC技術與估值延伸被比作dot-com泡沫風險。INTC不追高，半導體風險備忘。</t>
         </is>
@@ -2959,12 +3669,15 @@
       <c r="G15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Apple/Intel代工合作傳聞式報導：媒體稱Apple與Intel初步代工合作，政府可能推動，INTC大漲。因非官方公告，只能列入INTC/TSM/AAPL供應鏈觀察，不可直接加分。</t>
         </is>
@@ -3004,12 +3717,15 @@
       <c r="G16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Goldman：AI資料中心電力需求可能兩年翻倍。美國資料中心電力需求可能從約31GW增至66GW；電網、變壓器、施工週期成瓶頸。AI power bottleneck升級為一線主題。觀察CEG/VST/NRG/ETN/PWR/GEV/VRT。</t>
         </is>
@@ -3049,12 +3765,15 @@
       <c r="G17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>AI基礎建設從NVDA擴散到AMD/INTC/MU/GLW。AI inference、CPU、記憶體、光通訊受重估；BTIG警告SOX可能修正25-30%。主線確認但所有垂直急漲標的都要等回踩。</t>
         </is>
@@ -3094,12 +3813,15 @@
       <c r="G18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>MU記憶體拋物線式上漲：單日+15%左右，週漲近38%，月漲近84%；DRAM/NAND/HBM供需緊張。記憶體主線確認，但MU進入S3過熱，不追高。</t>
         </is>
@@ -3139,12 +3861,15 @@
       <c r="G19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Token demand inflation：CPU到雲服務。Agentic AI可能推升CPU、主機記憶體、DRAM、雲端伺服器需求。支持AMD/ARM/INTC/GOOGL/MSFT/AMZN的AI CPU子題材。</t>
         </is>
@@ -3184,12 +3909,15 @@
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>isolate</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>BBAT 2026 GPU採購預算傳聞：ByteDance、Tencent、Alibaba、Baidu GPU預算估算。只能作AI capex方向觀察，不可直接加分。</t>
         </is>
@@ -3229,12 +3957,15 @@
       <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>半導體狂熱接近2000泡沫警告。SOXL、AMD、記憶體、CPU、AI半導體全面擁擠；但AI需求仍是真實支撐。主線仍強但短線追高風險大。</t>
         </is>
@@ -3274,12 +4005,15 @@
       <c r="G22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>AI半導體輪動、NVDA-Corning、AMD等。AI半導體、光通訊、資料中心供應鏈持續強勢。支持AI infrastructure主線。</t>
         </is>
@@ -3319,12 +4053,15 @@
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>美股創高、SOX狂熱、Fed風險。S&amp;P/Nasdaq創新高，SOX大漲，MU/INTC/AMD/SNDK過熱；Roger Ferguson提到今年可能不排除升息。風險偏好強但半導體擁擠交易升高。</t>
         </is>
@@ -3364,12 +4101,15 @@
       <c r="G24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>4月非農就業資料：醫療、零售、休閒、運輸就業增加；製造、資訊、金融收縮。勞動市場韌性仍在，但不是明確降息利多。</t>
         </is>
@@ -3409,12 +4149,15 @@
       <c r="G25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>NFP高波動事件框架：2026年NFP波動大，單月數據不穩定，公布前不宜重倉押方向。NFP前禁止強推高波動標的。</t>
         </is>
@@ -3454,12 +4197,15 @@
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>沙烏地/科威特恢復美軍基地與空域通行。可能提高美國對Hormuz航線護航或軍事行動能力。油價、黃金、風險資產短線波動升高。</t>
         </is>
@@ -3499,12 +4245,15 @@
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>霍爾木茲風險、油價、航運通道可能影響市場。對高beta、小型股、航空、消費風險偏負面。</t>
         </is>
@@ -3544,12 +4293,15 @@
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>美國/伊朗談判不確定，中東局勢仍可能影響油價、航運、風險資產。屬地緣風險，不是直接買股理由。</t>
         </is>
@@ -3589,19 +4341,22 @@
       <c r="G29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>ADP就業韌性仍在，Fed降息預期降溫，油價與美元影響風險偏好。支持選擇性多頭，不是全面風險強攻。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:L29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/US_Alpha_Records.xlsx
+++ b/output/US_Alpha_Records.xlsx
@@ -19,27 +19,29 @@
     <sheet name="持倉管理" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="復盤紀錄" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="交易計畫" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="時間閘門" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="出場計畫" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="模型修正" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="環境記憶" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="當前持倉" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="時間閘門" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="出場計畫" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="模型修正" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="環境記憶" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推薦紀錄'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'評分審計'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'觀察名單'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'催化劑'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'資訊收錄'!$A$1:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'排除名單'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$T$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'復盤紀錄'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'時間閘門'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'出場計畫'!$A$1:$R$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'模型修正'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'排除名單'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$T$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'復盤紀錄'!$A$1:$AA$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$AI$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'當前持倉'!$A$1:$W$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'時間閘門'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'出場計畫'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'模型修正'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +50,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,7 +61,19 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -68,7 +82,7 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -81,12 +95,30 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -96,20 +128,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,30 +151,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00006100"/>
+          <bgColor rgb="00006100"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="009C0006"/>
+          <bgColor rgb="009C0006"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -516,298 +589,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>美股高報酬交易系統</t>
+          <t>美股高報酬交易決策系統 v2.2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>匯出時間：2026-05-10 05:26</t>
+          <t>匯出時間：2026-05-10 05:41</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.2 | TIMING + EXIT + TRADE_PLAN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>資料表統計</t>
+          <t>系統狀態</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>v2.2 合規檢查</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>資訊收錄</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>28</v>
       </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>TIMING_ENGINE 啟用</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>市場環境</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>市場環境紀錄</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>EXIT_ENGINE 啟用</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>板塊強度</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>8</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>板塊評分紀錄</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>TRADE_PLAN 完整</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>催化劑</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>催化劑追蹤</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>INFO_GATE 運作中</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>評分審計</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_GATE 運作中</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>正式推薦</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK 運作中</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>觀察名單</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>觀察名單（活躍）</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>RISK_LOCK 運作中</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>排除名單</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>3</v>
+      <c r="B12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SCORE_ENGINE 運作中</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>持倉管理</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>3</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>持倉動作歷史</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>REC_ENGINE 就緒</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>當前持倉</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>POSTMORTEM 就緒</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>復盤紀錄</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>模型修正</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>交易計畫</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>績效統計</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>風險控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>總推薦數</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>時間閘門</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>出場計畫</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>正式REC數量</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>A級主線板塊</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>勝利</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>報酬≥10%</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>B級強勢板塊</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>部分成功</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>報酬0-10%</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>風險封鎖數</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>虧損</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>報酬&lt;0%</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>活躍觀察名單</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>環境記憶</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>勝率</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>勝利/總數</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>當前持倉數</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>平均報酬</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>全部推薦平均</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>連續虧損</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>勝率統計</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>總推薦數</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>勝利</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>部分成功</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>0</v>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>平均MFE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>最大有利波動平均</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>虧損</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>勝率</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>平均MAE</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>平均報酬</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>最大不利波動平均</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>平均MFE</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>v2.2 核心紀律</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>平均MAE</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>1. 沒有 TIMING_GATE 通過，不可建立 REC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2. 沒有 EXIT_PLAN，不可建立 REC</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>系統版本</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>3. 沒有完整 TRADE_PLAN，不可建立 REC</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.2</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>4. RR &lt; 2.5:1 不主推</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>含：TIMING + EXIT + TRADE_PLAN</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>5. SEC 未通過直接封鎖</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>6. S3 過熱不追</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>7. 每日最多 3 支主推</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8. 反方論述必填</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>9. 寧可不推薦也不硬推</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>10. 每筆推薦都要可復盤</t>
         </is>
       </c>
     </row>
@@ -822,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -848,237 +1155,526 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>現價</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>持倉金額</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>盈虧%</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>推薦ID</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>買入理由</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>警戒價</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>失效價</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>停損價</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>可否加碼</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>加碼條件</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>持有天數</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>邏輯有效</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>下一步</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T16:00:00</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>reduce</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="10" t="n">
         <v>165.5</v>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="n">
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="5" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>MIST</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T16:00:00</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>hold</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="n">
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="10" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+      <c r="S3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
+      <c r="T3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>CRSR</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T16:00:00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>hold</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="10" t="n">
         <v>7.73</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="10" t="n">
         <v>7.88</v>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="n">
         <v>1.94</v>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="n">
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="n">
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="O4" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="n">
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="10" t="inlineStr"/>
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="5" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:00:00</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09T16:00:00</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="10" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr"/>
+      <c r="R6" s="10" t="inlineStr"/>
+      <c r="S6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09T16:00:00</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr"/>
+      <c r="R7" s="10" t="inlineStr"/>
+      <c r="S7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:00:00</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr"/>
+      <c r="P8" s="10" t="inlineStr"/>
+      <c r="Q8" s="10" t="inlineStr"/>
+      <c r="R8" s="10" t="inlineStr"/>
+      <c r="S8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09T16:00:00</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr"/>
+      <c r="P9" s="10" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr"/>
+      <c r="R9" s="10" t="inlineStr"/>
+      <c r="S9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09T16:00:00</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" s="10" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr"/>
+      <c r="R10" s="10" t="inlineStr"/>
+      <c r="S10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T4"/>
+  <autoFilter ref="A1:T10"/>
+  <conditionalFormatting sqref="H2:H10">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>-5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P10">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
+      <formula>"no"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R10">
+    <cfRule type="cellIs" priority="5" operator="lessThanOrEqual" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" dxfId="3">
+      <formula>4</formula>
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：hold,add,reduce,stop_loss,wait" type="list">
+      <formula1>"hold,add,reduce,stop_loss,wait"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：hold,add,reduce,exit,watch" type="list">
+      <formula1>"hold,add,reduce,exit,watch"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1089,75 +1685,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>推薦ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>評分ID</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>計畫ID</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>復盤日期</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>週期</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>進場價</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>停損</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>最高價</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>最低價</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>現價/出場價</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>MFE%</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>MAE%</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>實際報酬%</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>MFE%</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>MAE%</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>觸發T1</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>觸發T2</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>觸發停損</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>觸發時間停損</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>持有天數</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>出場觸發</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>錯誤類型</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>成功原因</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>失敗原因</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>需改模型</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>結論</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:AA1"/>
+  <dataValidations count="3">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：7d,30d,90d,180d,365d" type="list">
+      <formula1>"7d,30d,90d,180d,365d"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：stop_loss,time_stop,t1_hit,t2_hit,trailing_stop,catalyst_fail,structure_break,manual" type="list">
+      <formula1>"stop_loss,time_stop,t1_hit,t2_hit,trailing_stop,catalyst_fail,structure_break,manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：info_error,timing_error,chasing_error,sector_misjudge,risk_underestimate,catalyst_miss,market_turn,technical_fail,liquidity_misjudge,sec_dilution" type="list">
+      <formula1>"info_error,timing_error,chasing_error,sector_misjudge,risk_underestimate,catalyst_miss,market_turn,technical_fail,liquidity_misjudge,sec_dilution"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1168,99 +1877,540 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="8" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>推薦ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>進場觸發</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>進場方式</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>進場區間</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>禁追價</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>停損</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>目標1</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>目標2</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>失效條件</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>時間停損天</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>T1比例</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>T2比例</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>剩餘處理</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>移動停損</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>倉位</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>時間閘門</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>出場規則</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>反方論述</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>完整計畫</t>
-        </is>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>風險%</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>每股風險</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>RR比</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>催化日期</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>距事件天</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
+          <t>時間狀態</t>
+        </is>
+      </c>
+      <c r="AB1" s="9" t="inlineStr">
+        <is>
+          <t>Timing通過</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>反方論述1</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>反方論述2</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>反方論述3</t>
+        </is>
+      </c>
+      <c r="AF1" s="9" t="inlineStr">
+        <is>
+          <t>失效條件1</t>
+        </is>
+      </c>
+      <c r="AG1" s="9" t="inlineStr">
+        <is>
+          <t>失效條件2</t>
+        </is>
+      </c>
+      <c r="AH1" s="9" t="inlineStr">
+        <is>
+          <t>失效條件3</t>
+        </is>
+      </c>
+      <c r="AI1" s="9" t="inlineStr">
+        <is>
+          <t>v2.2合規</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr"/>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_v2.2</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>selective_bull</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>C級</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>回踩7.85+放量</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>限價</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>7.73-7.88</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.00</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>10EMA</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本;+10%上移</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>120股</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" s="10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="W2" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X2" s="10" t="inlineStr">
+        <is>
+          <t>PC/Gaming輪動</t>
+        </is>
+      </c>
+      <c r="Y2" s="10" t="inlineStr"/>
+      <c r="Z2" s="10" t="inlineStr"/>
+      <c r="AA2" s="10" t="inlineStr">
+        <is>
+          <t>T0_clear</t>
+        </is>
+      </c>
+      <c r="AB2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="10" t="inlineStr">
+        <is>
+          <t>板塊弱</t>
+        </is>
+      </c>
+      <c r="AD2" s="10" t="inlineStr">
+        <is>
+          <t>IWM偏弱</t>
+        </is>
+      </c>
+      <c r="AE2" s="10" t="inlineStr">
+        <is>
+          <t>量不足</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.20+量增</t>
+        </is>
+      </c>
+      <c r="AG2" s="10" t="inlineStr">
+        <is>
+          <t>10天無法破8.00</t>
+        </is>
+      </c>
+      <c r="AH2" s="10" t="inlineStr">
+        <is>
+          <t>IWM破支撐</t>
+        </is>
+      </c>
+      <c r="AI2" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr"/>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_v2.2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>selective_bull</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Electronics C級</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>回踩7.85支撐+放量確認</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>限價/回踩確認</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>7.73-7.88</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.00=主升邏輯失效</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>跟蹤10EMA</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本; +10%停損上移至成本+3%</t>
+        </is>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>120股</t>
+        </is>
+      </c>
+      <c r="U3" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V3" s="10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="W3" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X3" s="10" t="inlineStr">
+        <is>
+          <t>PC/Gaming硬體輪動+技術確認</t>
+        </is>
+      </c>
+      <c r="Y3" s="10" t="inlineStr"/>
+      <c r="Z3" s="10" t="inlineStr"/>
+      <c r="AA3" s="10" t="inlineStr">
+        <is>
+          <t>T0_clear</t>
+        </is>
+      </c>
+      <c r="AB3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="10" t="inlineStr">
+        <is>
+          <t>PC/Gaming板塊整體弱勢，CRSR只是短線反彈</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="inlineStr">
+        <is>
+          <t>小型股IWM偏弱，CRSR可能被大盤拖累</t>
+        </is>
+      </c>
+      <c r="AE3" s="10" t="inlineStr">
+        <is>
+          <t>成交量不足以支撐突破8.20</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.20+量增=波段失效</t>
+        </is>
+      </c>
+      <c r="AG3" s="10" t="inlineStr">
+        <is>
+          <t>10天內無法突破8.00=動能衰竭</t>
+        </is>
+      </c>
+      <c r="AH3" s="10" t="inlineStr">
+        <is>
+          <t>IWM跌破關鍵支撐=系統性風險</t>
+        </is>
+      </c>
+      <c r="AI3" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:AI3"/>
+  <conditionalFormatting sqref="Z2:Z3">
+    <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="3">
+      <formula>4</formula>
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB3">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI2:AI3">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1271,7 +2421,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:W3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>股數</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>現價</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>持倉金額</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>盈虧%</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>盈虧金額</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>進場日</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>持有天數</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>停損</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>警戒價</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>失效價</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>可加碼</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>加碼條件</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>移動停損</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>邏輯有效</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>動能狀態</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr"/>
+      <c r="D2" s="10" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>05-13事件後</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
+          <t>事件持倉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>945.6</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>盈利+回踩10EMA</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="U3" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="V3" s="10" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>守7.85-8.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:W3"/>
+  <conditionalFormatting sqref="G2:G3">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>-5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H3">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="1">
+      <formula>-5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J3">
+    <cfRule type="cellIs" priority="7" operator="lessThanOrEqual" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="between" dxfId="3">
+      <formula>4</formula>
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P3">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
+      <formula>"no"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：active,closed,stopped" type="list">
+      <formula1>"active,closed,stopped"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：hold,add,reduce,exit,watch" type="list">
+      <formula1>"hold,add,reduce,exit,watch"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：yes,no,conditional" type="list">
+      <formula1>"yes,no,conditional"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：S0-A,S0-B,S0-C,S1,S2,S3,S4" type="list">
+      <formula1>"S0-A,S0-B,S0-C,S1,S2,S3,S4"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1291,240 +2798,216 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>時間狀態</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>財報日期</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>距財報天數</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>催化劑日期</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>距事件天數</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>FOMC週</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>OPEX週</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>CPI/NFP</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>財報季</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>通過</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>T3_earnings_zone</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>T0_clear</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>無事件衝突</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>T0_clear</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>S3過熱+距財報遠，但市場進入財報季擁擠</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>MIST</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>T4_event_lockout</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>距財報4天，禁止追買，持有不加碼</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>T0_clear</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>無事件衝突，可正常操作</t>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>無事件衝突</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N3"/>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="3">
+      <formula>4</formula>
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G3">
+    <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="3">
+      <formula>4</formula>
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L3">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：T0_clear,T1_caution,T2_restricted,T3_earnings_zone,T4_event_lockout,T5_post_event" type="list">
+      <formula1>"T0_clear,T1_caution,T2_restricted,T3_earnings_zone,T4_event_lockout,T5_post_event"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：clear,reduce,delay,block" type="list">
+      <formula1>"clear,reduce,delay,block"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1548,230 +3031,110 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>推薦ID</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>進場價</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>停損</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>移動停損規則</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>T1出場比</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>T2出場比</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>剩餘部位</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>時間停損天數</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>利多出盡規則</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>結構失效規則</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>獲利鎖定規則</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>實際出場觸發</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>實際出場價</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>實際出場日</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>MIST</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr"/>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>事件後判斷</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>事件後確認方向再設</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>05-13事件後3天無正面反應=催化失效，快速退出</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>財報後跌破前低=結構失效</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr"/>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>+5%保本，+10%停損上移至7.73+3%</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>跟蹤10EMA</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>若10天內無法突破8.20則減倉</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>跌破7.20+量增=波段失效</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>+5%-&gt;保本; +10%-&gt;+3%; +15%-&gt;10EMA</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R3"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1782,147 +3145,363 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>修改模組</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>修改內容</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>觸發來源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>REC_ENGINE</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>v2.2正式執行：沒有Timing/Exit/Trade Plan不可建立REC</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>確保每筆推薦都有完整進出場計畫</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>MODEL-CHANGE-20260510-v2.2-001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>v2.2升級路線圖批准：新增TIMING_ENGINE、EXIT_ENGINE、TRADE_PLAN_TEMPLATE</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>系統從選股器升級為交易決策系統</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>SYS-20260510-001</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>HIGH_ALPHA_LAUNCHPAD</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>啟用v2.1：SEC排雷先行、催化不明不主推、RS&lt;70不主推、spread&gt;2%不主推、RR≥2.5:1</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>防止低品質推薦進入正式名單</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>SYS-20260508-002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>STRATEGY_ROUTER</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>建立富途四選股器：S0潛伏池/S1-A嚴格點火/S1-B寬版點火/S2續航池</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>系統化Futu掃描結果的分層與優先級</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>SYS-20260508-001</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>REC_ENGINE</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>v2.2正式執行：沒有Timing/Exit/Trade Plan不可建立REC</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>確保每筆推薦都有完整進出場計畫</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>MODEL-CHANGE-20260510-v2.2-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>v2.2升級路線圖批准：新增TIMING_ENGINE、EXIT_ENGINE、TRADE_PLAN_TEMPLATE</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>系統從選股器升級為交易決策系統</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260510-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_LAUNCHPAD</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>啟用v2.1：SEC排雷先行、催化不明不主推、RS&lt;70不主推、spread&gt;2%不主推、RR≥2.5:1</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>防止低品質推薦進入正式名單</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260508-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>STRATEGY_ROUTER</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>建立富途四選股器：S0潛伏池/S1-A嚴格點火/S1-B寬版點火/S2續航池</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>系統化Futu掃描結果的分層與優先級</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260508-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>REC_ENGINE</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>v2.2正式執行：沒有Timing/Exit/Trade Plan不可建立REC</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>確保每筆推薦都有完整進出場計畫</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>MODEL-CHANGE-20260510-v2.2-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>v2.2升級路線圖批准：新增TIMING_ENGINE、EXIT_ENGINE、TRADE_PLAN_TEMPLATE</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>系統從選股器升級為交易決策系統</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260510-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_LAUNCHPAD</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>啟用v2.1：SEC排雷先行、催化不明不主推、RS&lt;70不主推、spread&gt;2%不主推、RR≥2.5:1</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>防止低品質推薦進入正式名單</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260508-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>STRATEGY_ROUTER</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>建立富途四選股器：S0潛伏池/S1-A嚴格點火/S1-B寬版點火/S2續航池</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>系統化Futu掃描結果的分層與優先級</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>SYS-20260508-001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1943,47 +3522,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>環境ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>市場狀態</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>開始日期</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>結束日期</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>觸發原因</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>VIX變化</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>經驗教訓</t>
         </is>
@@ -2027,102 +3606,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>推薦ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>策略版本</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>動能狀態</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>推薦類型</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>買入價</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>停損</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>目標1</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>目標2</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>RR比</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>等級</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>市場狀態</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>倉位風險</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>富途優先</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>MFE%</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>MAE%</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>最終結果</t>
         </is>
@@ -2130,6 +3709,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
+  <dataValidations count="5">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A,B,C,D,F,P" type="list">
+      <formula1>"A,B,C,D,F,P"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：risk_on,selective_bull,neutral_range,risk_off,event_only" type="list">
+      <formula1>"risk_on,selective_bull,neutral_range,risk_off,event_only"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：S0-A,S0-B,S0-C,S1,S2,S3,S4" type="list">
+      <formula1>"S0-A,S0-B,S0-C,S1,S2,S3,S4"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：primary,secondary,small_event,continuation" type="list">
+      <formula1>"primary,secondary,small_event,continuation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：standard,half,small,forbidden" type="list">
+      <formula1>"standard,half,small,forbidden"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,47 +3751,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>評分ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>策略版本</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>原始分</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>最終分</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>等級</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>風險封鎖</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>進入推薦</t>
         </is>
@@ -2203,6 +3799,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A,B,C,D,F,P" type="list">
+      <formula1>"A,B,C,D,F,P"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：pass,warning,blocked" type="list">
+      <formula1>"pass,warning,blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2228,227 +3832,227 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>觀察ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>分層</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>觀察原因</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>未通過原因</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>觸發條件</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>可轉推薦</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>下次檢查</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>WATCH-20260509-004</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>TRAW</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>S1-A嚴格點火池</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>SEC/流動性/催化劑未查</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>通過排雷後再評估</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>WATCH-20260509-003</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>GCTS</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>S1-A嚴格點火池</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>SEC/流動性/催化劑未查</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>通過排雷後再評估</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>WATCH-20260509-002</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>VST</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>AI power主線代表</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>位置可能偏高</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>回踩確認</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>WATCH-20260509-001</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>CEG</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>AI data center power主線，Goldman報告確認</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>需確認是否已大幅反映</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>回踩20EMA支撐+放量</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
@@ -2456,6 +4060,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：core,standard,event,watch,pending,excluded" type="list">
+      <formula1>"core,standard,event,watch,pending,excluded"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2466,7 +4075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2481,95 +4090,182 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>市場狀態</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>SMH</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>10Y殖利率</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>selective_bull</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="10" t="n">
         <v>13.5</v>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>S&amp;P/Nasdaq創新高，SOX大漲，但IWM弱。選擇性多頭，不是全面風險強攻。半導體擁擠交易升高。</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>selective_bull</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>S&amp;P/Nasdaq創新高，SOX大漲，但IWM弱。選擇性多頭，不是全面風險強攻。半導體擁擠交易升高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>selective_bull</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>S&amp;P/Nasdaq創新高，SOX大漲，但IWM弱。選擇性多頭，不是全面風險強攻。半導體擁擠交易升高。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I4"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：risk_on,selective_bull,neutral_range,risk_off,event_only" type="list">
+      <formula1>"risk_on,selective_bull,neutral_range,risk_off,event_only"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2580,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2591,234 +4287,639 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>板塊</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>等級</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>代表股</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>["FTNT", "ZS", "CRWD", "PANW"]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Consumer Electronics / PC / Gaming</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>["CRSR", "LOGI"]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Biotech / Healthcare Events</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>["MIST", "MRNA", "REGN"]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>AI Data Center Power</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>["CEG", "VST", "NRG", "ETN", "VRT"]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>AI Software / Cloud / Agentic AI</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>["DDOG", "CRWD", "ZS", "FTNT"]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Memory / HBM / NAND / SSD</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>["MU", "WDC", "SNDK"]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Semiconductor / AI ASIC / Networking / CPO</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>["AVGO", "MRVL", "ANET", "COHR"]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>AI Infrastructure</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>["NVDA", "AVGO", "MRVL", "GLW"]</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>["FTNT", "ZS", "CRWD", "PANW"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Electronics / PC / Gaming</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>["CRSR", "LOGI"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Biotech / Healthcare Events</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>["MIST", "MRNA", "REGN"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>AI Data Center Power</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>["CEG", "VST", "NRG", "ETN", "VRT"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>AI Software / Cloud / Agentic AI</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>["DDOG", "CRWD", "ZS", "FTNT"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Memory / HBM / NAND / SSD</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>["MU", "WDC", "SNDK"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Semiconductor / AI ASIC / Networking / CPO</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>["AVGO", "MRVL", "ANET", "COHR"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>["NVDA", "AVGO", "MRVL", "GLW"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>["FTNT", "ZS", "CRWD", "PANW"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Electronics / PC / Gaming</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>["CRSR", "LOGI"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Biotech / Healthcare Events</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>["MIST", "MRNA", "REGN"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>AI Data Center Power</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>["CEG", "VST", "NRG", "ETN", "VRT"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>AI Software / Cloud / Agentic AI</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>["DDOG", "CRWD", "ZS", "FTNT"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Memory / HBM / NAND / SSD</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>["MU", "WDC", "SNDK"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Semiconductor / AI ASIC / Networking / CPO</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>["AVGO", "MRVL", "ANET", "COHR"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>["NVDA", "AVGO", "MRVL", "GLW"]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E25"/>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A,B,C,WEAK" type="list">
+      <formula1>"A,B,C,WEAK"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2840,81 +4941,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>催化劑ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>事件類型</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>預計日期</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>確定性</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>CAT-20260509-MU-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>earnings</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>CAT-20260509-MIST-001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MIST</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>earnings</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -2950,1406 +5051,1406 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>資訊ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>涉及股票</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>來源等級</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>進入主分數</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>進入市場閘門</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>進入風險封鎖</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>進入板塊分數</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>結論</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>內容摘要</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-SENTIMENT-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T16:00:00</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>["MU", "INTC", "AMD", "SMH"]</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>市場極度追逐AI/半導體：MU/INTC/AMD/SOX過熱，散戶與媒體關注升高。啟動SENTIMENT_GAUGE雛形：過熱冷卻，不追高。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-OPT-001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T16:00:00</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>["TSLA", "NKE", "RCL", "FLUT", "TPR", "SGI"]</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>消費可選股異常選擇權：TSLA/NKE/RCL/FLUT等出現bearish/neutral put或call flow；TPR/SGI有偏多流。選擇權流向歧義大，只能作情緒輔助，不可單獨做買賣依據。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-RPD-HOLD-001</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T15:00:00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>["RPD"]</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>RPD先前持倉成本6.80、155股；後續因公司展望弱被降級。若仍持有需重新提供最新股數與成本；舊邏輯已削弱。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-MRVL-001</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T13:00:00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>["MRVL"]</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>MRVL持倉盤中管理：仍有效但未breakout confirmed；167.4上方才可加碼。守165/164/162.8。後續已獲利+51.64美元稅費前。交易已關閉。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-CRSR-001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T15:00:00</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>["CRSR"]</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>CRSR進入S1-B/S2池。持倉120股，成本7.73；晚盤/收盤附近技術跟進至7.88。持有；8.20 T1，8.80-9.00 T2；7.20減倉/停損，7.00硬失效。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-MIST-001</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T14:00:00</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>["MIST"]</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>MIST IQVIA TRx：1月682、2月2947、3月9713、4月15876；但Q1 revenue $29.8M與TRx×ASP不一致。數據重要但未驗證；收入口徑有疑點；2026-05-13前不加碼。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-SCAN-002</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T11:00:00</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>["GCTS", "TRAW"]</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>S1-A嚴格點火：GCTS、TRAW短線爆發動能強。需要SEC/流動性/催化劑檢查，未通過前不主推。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-SCAN-001</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T10:30:00</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>["GRPN", "SHMD", "FNKO", "MX", "GCTS", "TRAW", "EVTV"]</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>富途區間漲幅/選股器結果：GRPN、SHMD、FNKO、MX、GCTS、TRAW、EVTV等進入S1/S2池。大多是高波動小票，只能逐檔排雷，不能直接推薦。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-HEATMAP-001</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T10:00:00</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>["SMH"]</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>富途熱力圖與板塊榜單：半導體、電腦硬體、半導體設備、太陽能強；軟體、醫療、廣告偏弱。板塊主線偏硬體，但多數已過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-083</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T14:30:00</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>["RPD"]</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>Rapid7分析師與財報電話會議：RPD Q1略優但ARR近乎持平，FY2026營收預期下滑，多家券商降目標價。RPD從可交易候選降為C+/B-，只能hold-only/watch，不可加碼。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-078</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T13:30:00</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>["DDOG", "FTNT", "ZS", "ARM", "IWM"]</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>IBD盤中更新：軟體強，半導體分化，小型股弱。DDOG/FTNT/ZS強，ARM/SNDK弱，小型股IWM弱。軟體/網安升溫，但小型股不能激進。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-077</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T13:00:00</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>["DDOG", "FTNT", "ZS", "CRWD"]</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>AI生產力、Agentic AI、雲端/軟體牛市。AI推升生產力，agentic AI、雲端、軟體應用受益。支持AI software/cloud/cybersecurity輪動。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-067</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T16:00:00</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>["INTC"]</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>Intel類Cisco泡沫警告：INTC技術與估值延伸被比作dot-com泡沫風險。INTC不追高，半導體風險備忘。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-INTC-APPLE-001</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T14:00:00</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>["INTC", "AAPL", "TSM"]</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>Apple/Intel代工合作傳聞式報導：媒體稱Apple與Intel初步代工合作，政府可能推動，INTC大漲。因非官方公告，只能列入INTC/TSM/AAPL供應鏈觀察，不可直接加分。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-POWER-001</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T12:00:00</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>["CEG", "VST", "NRG", "ETN", "PWR", "GEV", "VRT"]</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="10" t="inlineStr">
         <is>
           <t>Goldman：AI資料中心電力需求可能兩年翻倍。美國資料中心電力需求可能從約31GW增至66GW；電網、變壓器、施工週期成瓶頸。AI power bottleneck升級為一線主題。觀察CEG/VST/NRG/ETN/PWR/GEV/VRT。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-AIHARDWARE-001</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T11:00:00</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>["NVDA", "AMD", "INTC", "MU", "GLW"]</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>AI基礎建設從NVDA擴散到AMD/INTC/MU/GLW。AI inference、CPU、記憶體、光通訊受重估；BTIG警告SOX可能修正25-30%。主線確認但所有垂直急漲標的都要等回踩。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-MU-001</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T10:00:00</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>["MU"]</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="10" t="inlineStr">
         <is>
           <t>MU記憶體拋物線式上漲：單日+15%左右，週漲近38%，月漲近84%；DRAM/NAND/HBM供需緊張。記憶體主線確認，但MU進入S3過熱，不追高。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-CPU-CLOUD-001</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T15:30:00</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>["AMD", "ARM", "INTC", "GOOGL", "MSFT", "AMZN"]</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>Token demand inflation：CPU到雲服務。Agentic AI可能推升CPU、主機記憶體、DRAM、雲端伺服器需求。支持AMD/ARM/INTC/GOOGL/MSFT/AMZN的AI CPU子題材。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-GPU-BUDGET-001</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T15:00:00</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>["NVDA", "AMD"]</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>isolate</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>BBAT 2026 GPU採購預算傳聞：ByteDance、Tencent、Alibaba、Baidu GPU預算估算。只能作AI capex方向觀察，不可直接加分。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-SEMI-OVERHEAT-001</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T14:00:00</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>["SMH", "AMD", "MU", "INTC"]</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>半導體狂熱接近2000泡沫警告。SOXL、AMD、記憶體、CPU、AI半導體全面擁擠；但AI需求仍是真實支撐。主線仍強但短線追高風險大。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-002</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T09:30:00</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>["NVDA", "AMD", "GLW", "AVGO"]</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>AI半導體輪動、NVDA-Corning、AMD等。AI半導體、光通訊、資料中心供應鏈持續強勢。支持AI infrastructure主線。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>INFO-20260509-MKT-001</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>2026-05-09T09:00:00</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>["SPY", "QQQ", "SMH", "MU", "INTC", "AMD"]</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>美股創高、SOX狂熱、Fed風險。S&amp;P/Nasdaq創新高，SOX大漲，MU/INTC/AMD/SNDK過熱；Roger Ferguson提到今年可能不排除升息。風險偏好強但半導體擁擠交易升高。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>INFO-20260508-NFP-001</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T09:30:00</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>["SPY"]</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>4月非農就業資料：醫療、零售、休閒、運輸就業增加；製造、資訊、金融收縮。勞動市場韌性仍在，但不是明確降息利多。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>BATCH-20260508-PRE-002</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>2026-05-08T08:00:00</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>["SPY", "QQQ", "IWM"]</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>NFP高波動事件框架：2026年NFP波動大，單月數據不穩定，公布前不宜重倉押方向。NFP前禁止強推高波動標的。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-HORMUZ-002</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T11:00:00</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>沙烏地/科威特恢復美軍基地與空域通行。可能提高美國對Hormuz航線護航或軍事行動能力。油價、黃金、風險資產短線波動升高。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-006</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T10:30:00</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>霍爾木茲風險、油價、航運通道可能影響市場。對高beta、小型股、航空、消費風險偏負面。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-005</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T10:00:00</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>observe</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>美國/伊朗談判不確定，中東局勢仍可能影響油價、航運、風險資產。屬地緣風險，不是直接買股理由。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>INFO-20260507-004</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>2026-05-07T09:00:00</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>["SPY", "QQQ"]</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>adopt</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>ADP就業韌性仍在，Fed降息預期降溫，油價與美元影響風險偏好。支持選擇性多頭，不是全面風險強攻。</t>
         </is>
@@ -4357,6 +6458,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L29"/>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A1,A2,B,C,R,UNKNOWN" type="list">
+      <formula1>"A1,A2,B,C,R,UNKNOWN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：bullish,bearish,neutral,uncertain" type="list">
+      <formula1>"bullish,bearish,neutral,uncertain"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：adopt,observe,isolate,exclude" type="list">
+      <formula1>"adopt,observe,isolate,exclude"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4367,7 +6479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4378,115 +6490,277 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>股票</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>排除原因</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>SOX整體過熱，AMD延伸過快</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>overheated</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>until_pullback</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>類Cisco泡沫警告+Apple代工未確認+垂直噴出</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>overheated</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>until_pullback</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>S3過熱：單日+15%，週+38%，月+84%</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>overheated</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>until_pullback</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>SOX整體過熱，AMD延伸過快</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>類Cisco泡沫警告+Apple代工未確認+垂直噴出</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>S3過熱：單日+15%，週+38%，月+84%</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>SOX整體過熱，AMD延伸過快</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>類Cisco泡沫警告+Apple代工未確認+垂直噴出</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>S3過熱：單日+15%，週+38%，月+84%</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>overheated</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>until_pullback</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/US_Alpha_Records.xlsx
+++ b/output/US_Alpha_Records.xlsx
@@ -23,25 +23,39 @@
     <sheet name="時間閘門" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="出場計畫" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="模型修正" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="環境記憶" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="相關性檢查" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="倉位計算" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="禁止交易區" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="偏誤檢查" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="決策疲勞" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="勝率儀表板" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="觀察名單結果" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="環境記憶" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推薦紀錄'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'評分審計'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'觀察名單'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'催化劑'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'資訊收錄'!$A$1:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'排除名單'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$T$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'排除名單'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'持倉管理'!$A$1:$T$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'復盤紀錄'!$A$1:$AA$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$AI$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$AI$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'當前持倉'!$A$1:$W$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'時間閘門'!$A$1:$N$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'出場計畫'!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'模型修正'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'出場計畫'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'模型修正'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'相關性檢查'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'倉位計算'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'禁止交易區'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'偏誤檢查'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'決策疲勞'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'勝率儀表板'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'觀察名單結果'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'環境記憶'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,8 +173,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -589,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -602,19 +616,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>美股高報酬交易決策系統 v2.2</t>
+          <t>美股高報酬交易決策系統 v2.5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>匯出時間：2026-05-10 05:41</t>
+          <t>匯出時間：2026-05-10 05:55</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.2 | TIMING + EXIT + TRADE_PLAN</t>
+          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.5 | TIMING + EXIT + CORRELATION + BIAS + WIN_RATE</t>
         </is>
       </c>
     </row>
@@ -641,7 +655,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>TIMING_ENGINE 啟用</t>
+          <t>v2.1 INFO_GATE</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -653,35 +667,35 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>市場環境紀錄</t>
+          <t>市場環境</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>EXIT_ENGINE 啟用</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>✗ 未啟用</t>
+          <t>v2.1 MARKET_GATE</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>✓ 已啟用</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>板塊評分紀錄</t>
+          <t>板塊評分</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>TRADE_PLAN 完整</t>
+          <t>v2.1 SECTOR_RANK</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -693,7 +707,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>催化劑追蹤</t>
+          <t>催化劑</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -701,7 +715,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>INFO_GATE 運作中</t>
+          <t>v2.1 RISK_LOCK</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -716,12 +730,12 @@
           <t>評分審計</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>MARKET_GATE 運作中</t>
+          <t>v2.2 TIMING_ENGINE</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -736,12 +750,12 @@
           <t>正式推薦</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SECTOR_RANK 運作中</t>
+          <t>v2.2 EXIT_ENGINE</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -753,7 +767,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>觀察名單（活躍）</t>
+          <t>觀察名單</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -761,7 +775,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>RISK_LOCK 運作中</t>
+          <t>v2.2 TRADE_PLAN</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -773,18 +787,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>排除名單</t>
+          <t>排除/封鎖</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SCORE_ENGINE 運作中</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
+          <t>v2.3 CORRELATION_GUARD</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>✗ 未啟用</t>
         </is>
@@ -793,20 +807,20 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>持倉動作歷史</t>
+          <t>持倉歷史</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>REC_ENGINE 就緒</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>✓ 已啟用</t>
+          <t>v2.3 POSITION_SIZING</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
         </is>
       </c>
     </row>
@@ -821,12 +835,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>POSTMORTEM 就緒</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>✓ 已啟用</t>
+          <t>v2.4 BIAS_FILTER</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
         </is>
       </c>
     </row>
@@ -836,8 +850,18 @@
           <t>復盤紀錄</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>v2.4 FATIGUE_GUARD</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -847,135 +871,111 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>v2.5 WIN_RATE_DASHBOARD</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>績效統計</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>交易計畫</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>風險控制</t>
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>v2.5 WATCHLIST_OUTCOME</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>總推薦數</t>
+          <t>時間閘門</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>正式REC數量</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>A級主線板塊</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>6</v>
+          <t>v2.5 REGIME_MEMORY</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>✗ 未啟用</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>勝利</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>報酬≥10%</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>B級強勢板塊</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>6</v>
+          <t>出場計畫</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>部分成功</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
+          <t>相關性檢查</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>報酬0-10%</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>風險封鎖數</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>虧損</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>績效統計</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>報酬&lt;0%</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>活躍觀察名單</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>2</v>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>風險控制</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>勝率</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>總推薦數</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>勝利/總數</t>
+          <t>正式REC數量</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>當前持倉數</t>
+          <t>A級主線板塊</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -985,136 +985,244 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>平均報酬</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>勝利</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>全部推薦平均</t>
+          <t>報酬≥10%</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>連續虧損</t>
+          <t>B級強勢板塊</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>平均MFE</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>部分成功</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>最大有利波動平均</t>
-        </is>
+          <t>報酬0-10%</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>風險封鎖數</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>平均MAE</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+          <t>虧損</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>報酬&lt;0%</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>活躍觀察名單</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>勝率</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>最大不利波動平均</t>
-        </is>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>勝利/總數</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>當前持倉數</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>平均報酬</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>全部推薦平均</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>連續虧損</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>v2.2 核心紀律</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>平均MFE</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>最大有利波動平均</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1. 沒有 TIMING_GATE 通過，不可建立 REC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2. 沒有 EXIT_PLAN，不可建立 REC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>3. 沒有完整 TRADE_PLAN，不可建立 REC</t>
+          <t>平均MAE</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>最大不利波動平均</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>4. RR &lt; 2.5:1 不主推</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>v2.5 核心紀律</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>5. SEC 未通過直接封鎖</t>
+          <t>1. 沒有 TIMING_GATE 通過，不可建立 REC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>6. S3 過熱不追</t>
+          <t>2. 沒有 EXIT_PLAN，不可建立 REC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>7. 每日最多 3 支主推</t>
+          <t>3. 沒有完整 TRADE_PLAN（含反方論述），不可建立 REC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>8. 反方論述必填</t>
+          <t>4. RR &lt; 2.5:1 不主推</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>9. 寧可不推薦也不硬推</t>
+          <t>5. SEC 未通過直接封鎖</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>10. 每筆推薦都要可復盤</t>
+          <t>6. S3 過熱不追</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>7. 每日最多 3 支主推（FATIGUE_GUARD）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>8. 同板塊不超過 2 支主推（CORRELATION_GUARD）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>9. 已持倉重新評分自動扣 5 分（BIAS_FILTER）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>10. 2 連虧只做 A 級；3 連虧暫停</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>11. 寧可不推薦也不硬推</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>12. 每筆推薦都要可復盤、可追蹤 ID 鏈</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1384,265 +1492,9 @@
       </c>
       <c r="T4" s="10" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08T16:00:00</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>165.5</v>
-      </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>MIST</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09T16:00:00</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr"/>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09T16:00:00</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr"/>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08T16:00:00</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>165.5</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr"/>
-      <c r="P8" s="10" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr"/>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>MIST</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09T16:00:00</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="10" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr"/>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09T16:00:00</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" s="10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="P10" s="10" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr"/>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T10"/>
-  <conditionalFormatting sqref="H2:H10">
+  <autoFilter ref="A1:T4"/>
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -1653,12 +1505,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
       <formula>"no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="cellIs" priority="5" operator="lessThanOrEqual" dxfId="2">
       <formula>3</formula>
     </cfRule>
@@ -1877,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2108,7 +1960,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>HIGH_ALPHA_v2.2</t>
+          <t>HIGH_ALPHA_v2.5</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -2116,40 +1968,20 @@
           <t>selective_bull</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>C級</t>
-        </is>
-      </c>
+      <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>回踩7.85+放量</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>限價</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>7.73-7.88</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>8.1</v>
-      </c>
+          <t>回踩7.85</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>跌破7.00</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="n">
-        <v>10</v>
-      </c>
+      <c r="L2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
       <c r="N2" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -2166,35 +1998,15 @@
           <t>1/3</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr">
-        <is>
-          <t>10EMA</t>
-        </is>
-      </c>
-      <c r="S2" s="10" t="inlineStr">
-        <is>
-          <t>+5%保本;+10%上移</t>
-        </is>
-      </c>
-      <c r="T2" s="10" t="inlineStr">
-        <is>
-          <t>120股</t>
-        </is>
-      </c>
-      <c r="U2" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V2" s="10" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
+      <c r="U2" s="10" t="inlineStr"/>
+      <c r="V2" s="10" t="inlineStr"/>
       <c r="W2" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="X2" s="10" t="inlineStr">
-        <is>
-          <t>PC/Gaming輪動</t>
-        </is>
-      </c>
+      <c r="X2" s="10" t="inlineStr"/>
       <c r="Y2" s="10" t="inlineStr"/>
       <c r="Z2" s="10" t="inlineStr"/>
       <c r="AA2" s="10" t="inlineStr">
@@ -2212,7 +2024,7 @@
       </c>
       <c r="AD2" s="10" t="inlineStr">
         <is>
-          <t>IWM偏弱</t>
+          <t>IWM弱</t>
         </is>
       </c>
       <c r="AE2" s="10" t="inlineStr">
@@ -2222,171 +2034,26 @@
       </c>
       <c r="AF2" s="10" t="inlineStr">
         <is>
-          <t>跌破7.20+量增</t>
+          <t>跌破7.20</t>
         </is>
       </c>
       <c r="AG2" s="10" t="inlineStr">
         <is>
-          <t>10天無法破8.00</t>
+          <t>10天無法破8</t>
         </is>
       </c>
       <c r="AH2" s="10" t="inlineStr">
         <is>
-          <t>IWM破支撐</t>
+          <t>IWM破位</t>
         </is>
       </c>
       <c r="AI2" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr"/>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>HIGH_ALPHA_v2.2</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>selective_bull</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Electronics C級</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>回踩7.85支撐+放量確認</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>限價/回踩確認</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>7.73-7.88</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>跌破7.00=主升邏輯失效</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" s="10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="10" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="inlineStr">
-        <is>
-          <t>跟蹤10EMA</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>+5%保本; +10%停損上移至成本+3%</t>
-        </is>
-      </c>
-      <c r="T3" s="10" t="inlineStr">
-        <is>
-          <t>120股</t>
-        </is>
-      </c>
-      <c r="U3" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V3" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="W3" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X3" s="10" t="inlineStr">
-        <is>
-          <t>PC/Gaming硬體輪動+技術確認</t>
-        </is>
-      </c>
-      <c r="Y3" s="10" t="inlineStr"/>
-      <c r="Z3" s="10" t="inlineStr"/>
-      <c r="AA3" s="10" t="inlineStr">
-        <is>
-          <t>T0_clear</t>
-        </is>
-      </c>
-      <c r="AB3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="10" t="inlineStr">
-        <is>
-          <t>PC/Gaming板塊整體弱勢，CRSR只是短線反彈</t>
-        </is>
-      </c>
-      <c r="AD3" s="10" t="inlineStr">
-        <is>
-          <t>小型股IWM偏弱，CRSR可能被大盤拖累</t>
-        </is>
-      </c>
-      <c r="AE3" s="10" t="inlineStr">
-        <is>
-          <t>成交量不足以支撐突破8.20</t>
-        </is>
-      </c>
-      <c r="AF3" s="10" t="inlineStr">
-        <is>
-          <t>跌破7.20+量增=波段失效</t>
-        </is>
-      </c>
-      <c r="AG3" s="10" t="inlineStr">
-        <is>
-          <t>10天內無法突破8.00=動能衰竭</t>
-        </is>
-      </c>
-      <c r="AH3" s="10" t="inlineStr">
-        <is>
-          <t>IWM跌破關鍵支撐=系統性風險</t>
-        </is>
-      </c>
-      <c r="AI3" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AI3"/>
-  <conditionalFormatting sqref="Z2:Z3">
+  <autoFilter ref="A1:AI2"/>
+  <conditionalFormatting sqref="Z2">
     <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="2">
       <formula>3</formula>
     </cfRule>
@@ -2395,7 +2062,7 @@
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB3">
+  <conditionalFormatting sqref="AB2">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -2403,7 +2070,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI3">
+  <conditionalFormatting sqref="AI2">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -2597,7 +2264,7 @@
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>05-13事件後</t>
+          <t>05-13後</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr"/>
@@ -2651,9 +2318,7 @@
       <c r="G3" s="10" t="n">
         <v>1.94</v>
       </c>
-      <c r="H3" s="10" t="n">
-        <v>18</v>
-      </c>
+      <c r="H3" s="10" t="inlineStr"/>
       <c r="I3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
@@ -2872,7 +2537,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>MIST</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -2882,11 +2547,17 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>T0_clear</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr"/>
+          <t>T4_event_lockout</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr"/>
       <c r="H2" s="10" t="n">
@@ -2902,18 +2573,14 @@
         <v>0</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>無事件衝突</t>
-        </is>
-      </c>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -2955,11 +2622,7 @@
           <t>clear</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>無事件衝突</t>
-        </is>
-      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N3"/>
@@ -3007,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3122,8 +2785,66 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr"/>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>10EMA</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本;+10%+3%</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:R2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3134,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3279,224 +3000,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>REC_ENGINE</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>v2.2正式執行：沒有Timing/Exit/Trade Plan不可建立REC</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>確保每筆推薦都有完整進出場計畫</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>MODEL-CHANGE-20260510-v2.2-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>SYSTEM</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>v2.2升級路線圖批准：新增TIMING_ENGINE、EXIT_ENGINE、TRADE_PLAN_TEMPLATE</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>系統從選股器升級為交易決策系統</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260510-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>HIGH_ALPHA_LAUNCHPAD</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>啟用v2.1：SEC排雷先行、催化不明不主推、RS&lt;70不主推、spread&gt;2%不主推、RR≥2.5:1</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>防止低品質推薦進入正式名單</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260508-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>STRATEGY_ROUTER</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>建立富途四選股器：S0潛伏池/S1-A嚴格點火/S1-B寬版點火/S2續航池</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>系統化Futu掃描結果的分層與優先級</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260508-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>REC_ENGINE</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>v2.2正式執行：沒有Timing/Exit/Trade Plan不可建立REC</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>確保每筆推薦都有完整進出場計畫</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>MODEL-CHANGE-20260510-v2.2-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>SYSTEM</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>v2.2升級路線圖批准：新增TIMING_ENGINE、EXIT_ENGINE、TRADE_PLAN_TEMPLATE</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>系統從選股器升級為交易決策系統</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260510-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>HIGH_ALPHA_LAUNCHPAD</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>啟用v2.1：SEC排雷先行、催化不明不主推、RS&lt;70不主推、spread&gt;2%不主推、RR≥2.5:1</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>防止低品質推薦進入正式名單</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260508-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>STRATEGY_ROUTER</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>建立富途四選股器：S0潛伏池/S1-A嚴格點火/S1-B寬版點火/S2續航池</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>系統化Futu掃描結果的分層與優先級</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>SYS-20260508-001</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3510,66 +3015,230 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>環境ID</t>
+          <t>檢查ID</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>市場狀態</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>開始日期</t>
+          <t>組合標的</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>結束日期</t>
+          <t>同板塊數</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>觸發原因</t>
+          <t>最高相關係數</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>同催化劑暴露</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>組合Beta</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>VIX變化</t>
+          <t>集中度判定</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>經驗教訓</t>
+          <t>最大總倉位</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>計算ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>帳戶總值</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>風險%</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>進場價</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>停損</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>每股風險</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>計算股數</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>倉位金額</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>佔帳戶%</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>交易類型</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>倉位判定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>禁區ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>影響標的</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>開始日</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>結束日</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>活躍</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3730,6 +3399,431 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>檢查ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>已持倉</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>持倉扣分</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>全部利多</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>過度一致</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>社群一致</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>媒體炒作</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>有反方論述</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>偏誤判定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>疲勞ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>今日推薦數</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>上限</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>連續虧損</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>今日虧損數</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>冷卻中</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>疲勞判定</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>允許等級</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>快照日期</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>總推薦</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>勝利</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>虧損</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>勝率%</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>T1命中%</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>T2命中%</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>停損率%</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>平均報酬%</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>平均MFE%</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>平均MAE%</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>賺賠比</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>最佳策略</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>最佳板塊</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>樣本充足</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>觀察ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>原始日期</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>結果日期</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>轉推薦</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>推薦ID</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>錯過</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>錯過漲幅%</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>偽陰性</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>環境ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>市場狀態</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>開始日期</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>結束日期</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>觸發原因</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>VIX變化</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>經驗教訓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4075,7 +4169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4177,90 +4271,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>selective_bull</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>S&amp;P/Nasdaq創新高，SOX大漲，但IWM弱。選擇性多頭，不是全面風險強攻。半導體擁擠交易升高。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>selective_bull</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>S&amp;P/Nasdaq創新高，SOX大漲，但IWM弱。選擇性多頭，不是全面風險強攻。半導體擁擠交易升高。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I2"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：risk_on,selective_bull,neutral_range,risk_off,event_only" type="list">
       <formula1>"risk_on,selective_bull,neutral_range,risk_off,event_only"</formula1>
@@ -4276,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4513,408 +4525,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>["FTNT", "ZS", "CRWD", "PANW"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Electronics / PC / Gaming</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>["CRSR", "LOGI"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Biotech / Healthcare Events</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>["MIST", "MRNA", "REGN"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>AI Data Center Power</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>["CEG", "VST", "NRG", "ETN", "VRT"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>AI Software / Cloud / Agentic AI</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>["DDOG", "CRWD", "ZS", "FTNT"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Memory / HBM / NAND / SSD</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>["MU", "WDC", "SNDK"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Semiconductor / AI ASIC / Networking / CPO</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>["AVGO", "MRVL", "ANET", "COHR"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>93</v>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>["NVDA", "AVGO", "MRVL", "GLW"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>["FTNT", "ZS", "CRWD", "PANW"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Electronics / PC / Gaming</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>["CRSR", "LOGI"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Biotech / Healthcare Events</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>["MIST", "MRNA", "REGN"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>AI Data Center Power</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>["CEG", "VST", "NRG", "ETN", "VRT"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>AI Software / Cloud / Agentic AI</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>["DDOG", "CRWD", "ZS", "FTNT"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Memory / HBM / NAND / SSD</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>["MU", "WDC", "SNDK"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Semiconductor / AI ASIC / Networking / CPO</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>["AVGO", "MRVL", "ANET", "COHR"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>93</v>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>["NVDA", "AVGO", "MRVL", "GLW"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E9"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A,B,C,WEAK" type="list">
       <formula1>"A,B,C,WEAK"</formula1>
@@ -6479,7 +6091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6597,170 +6209,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>SOX整體過熱，AMD延伸過快</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>類Cisco泡沫警告+Apple代工未確認+垂直噴出</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>S3過熱：單日+15%，週+38%，月+84%</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>SOX整體過熱，AMD延伸過快</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>類Cisco泡沫警告+Apple代工未確認+垂直噴出</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>S3過熱：單日+15%，週+38%，月+84%</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>overheated</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>until_pullback</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/US_Alpha_Records.xlsx
+++ b/output/US_Alpha_Records.xlsx
@@ -31,11 +31,13 @@
     <sheet name="勝率儀表板" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="觀察名單結果" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="環境記憶" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="ID鏈檢查" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="資料字典" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推薦紀錄'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'評分審計'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'觀察名單'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'評分審計'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'觀察名單'!$A$1:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'市場環境'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'板塊強度'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'催化劑'!$A$1:$E$3</definedName>
@@ -46,7 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'交易計畫'!$A$1:$AI$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'當前持倉'!$A$1:$W$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'時間閘門'!$A$1:$N$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'出場計畫'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'出場計畫'!$A$1:$R$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'模型修正'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'相關性檢查'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'倉位計算'!$A$1:$M$1</definedName>
@@ -165,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +192,11 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -623,7 +630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>匯出時間：2026-05-10 05:55</t>
+          <t>匯出時間：2026-05-10 06:06</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -730,8 +737,8 @@
           <t>評分審計</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>0</v>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -771,7 +778,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -931,7 +938,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1048,7 +1055,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1960,7 +1967,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>HIGH_ALPHA_v2.5</t>
+          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.5</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -1968,20 +1975,40 @@
           <t>selective_bull</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Electronics C級(47/100)</t>
+        </is>
+      </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>回踩7.85</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+          <t>回踩7.85支撐+縮量後放量確認</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>限價/回踩確認</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>7.73-7.88</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>8.1</v>
+      </c>
       <c r="K2" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.00=S1主升邏輯失效</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="N2" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -1998,15 +2025,35 @@
           <t>1/3</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>跟蹤10EMA</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本; +10%上移至成本+3%; +15%跟10EMA</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>120股 ($945)</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" s="10" t="n">
+        <v>0.73</v>
+      </c>
       <c r="W2" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="X2" s="10" t="inlineStr"/>
+      <c r="X2" s="10" t="inlineStr">
+        <is>
+          <t>PC/Gaming硬體輪動+S1-B/S2交叉+技術確認</t>
+        </is>
+      </c>
       <c r="Y2" s="10" t="inlineStr"/>
       <c r="Z2" s="10" t="inlineStr"/>
       <c r="AA2" s="10" t="inlineStr">
@@ -2019,32 +2066,32 @@
       </c>
       <c r="AC2" s="10" t="inlineStr">
         <is>
-          <t>板塊弱</t>
+          <t>PC/Gaming板塊整體弱勢(C級47分)，CRSR可能只是短線反彈而非趨勢反轉</t>
         </is>
       </c>
       <c r="AD2" s="10" t="inlineStr">
         <is>
-          <t>IWM弱</t>
+          <t>小型股IWM偏弱，系統性風險可能拖累CRSR即使個股邏輯成立</t>
         </is>
       </c>
       <c r="AE2" s="10" t="inlineStr">
         <is>
-          <t>量不足</t>
+          <t>成交量可能不足以支撐有效突破8.20，動能在8.00附近衰竭</t>
         </is>
       </c>
       <c r="AF2" s="10" t="inlineStr">
         <is>
-          <t>跌破7.20</t>
+          <t>跌破7.20 + 成交量放大 = 波段結構失效，全部退出</t>
         </is>
       </c>
       <c r="AG2" s="10" t="inlineStr">
         <is>
-          <t>10天無法破8</t>
+          <t>10個交易日內無法有效突破8.00 = 動能衰竭，減倉50%</t>
         </is>
       </c>
       <c r="AH2" s="10" t="inlineStr">
         <is>
-          <t>IWM破位</t>
+          <t>IWM跌破關鍵支撐 = 小型股系統性風險升高，降低所有小票倉位</t>
         </is>
       </c>
       <c r="AI2" s="10" t="n">
@@ -2264,10 +2311,14 @@
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>05-13後</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="inlineStr"/>
+          <t>05-13事件後確認數據一致性才可決定</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>事件後設定</t>
+        </is>
+      </c>
       <c r="S2" s="10" t="n">
         <v>1</v>
       </c>
@@ -2278,7 +2329,7 @@
       </c>
       <c r="U2" s="10" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Biotech / Healthcare Events</t>
         </is>
       </c>
       <c r="V2" s="10" t="inlineStr">
@@ -2288,7 +2339,7 @@
       </c>
       <c r="W2" s="10" t="inlineStr">
         <is>
-          <t>事件持倉</t>
+          <t>事件持倉；TRx數據正面但Q1 revenue口徑有矛盾；05-13前不加碼不減碼；等官方確認</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2369,9 @@
       <c r="G3" s="10" t="n">
         <v>1.94</v>
       </c>
-      <c r="H3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
           <t>2026-05-09</t>
@@ -2349,7 +2402,7 @@
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>盈利+回踩10EMA</t>
+          <t>已盈利+回踩10EMA成功+量縮</t>
         </is>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -2367,7 +2420,7 @@
       </c>
       <c r="U3" s="10" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Consumer Electronics / PC / Gaming</t>
         </is>
       </c>
       <c r="V3" s="10" t="inlineStr">
@@ -2377,7 +2430,7 @@
       </c>
       <c r="W3" s="10" t="inlineStr">
         <is>
-          <t>守7.85-8.00</t>
+          <t>不追高；守7.85-8.00；突破8.20才升級為正式REC</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2633,11 @@
           <t>block</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>距財報/事件3天，禁止追買，持有不加碼。事件後判斷利多是否出盡。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -2622,7 +2679,11 @@
           <t>clear</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>無財報/FOMC/OPEX衝突，時間閘門通過</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N3"/>
@@ -2670,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2788,7 +2849,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>MIST</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr"/>
@@ -2797,28 +2858,20 @@
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="D2" s="10" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr"/>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>+5%保本</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>8.199999999999999</v>
-      </c>
+          <t>事件後確認方向再設定移動停損</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr"/>
       <c r="H2" s="10" t="inlineStr">
         <is>
           <t>1/3</t>
         </is>
       </c>
-      <c r="I2" s="10" t="n">
-        <v>9</v>
-      </c>
+      <c r="I2" s="10" t="inlineStr"/>
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>1/3</t>
@@ -2826,25 +2879,99 @@
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>10EMA</t>
+          <t>事件後確認方向再設</t>
         </is>
       </c>
       <c r="L2" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>05-13事件後3天內無正面股價反應=催化失效，快速全部退出</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>財報後跌破前低=結構失效，不論原因立即退出</t>
+        </is>
+      </c>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>+5%保本;+10%+3%</t>
+          <t>事件後若跳空上漲&gt;15%，第一天出1/3鎖定利潤</t>
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr"/>
       <c r="Q2" s="10" t="inlineStr"/>
       <c r="R2" s="10" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>+5%保本(8.12); +10%停損上移至成本+3%(7.96); +15%跟蹤10EMA</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>跟蹤10EMA，跌破即全出</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>10天內無法突破8.20=動能衰竭，減倉至50%</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>跌破7.20+量增=波段結構失效，全部退出</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>+5%→保本; +10%→+3%; +15%→10EMA; +20%→前波段低點</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R2"/>
+  <autoFilter ref="A1:R3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3824,13 +3951,796 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>INFO_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>SCORE_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>WATCH/REC_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>PLAN_ID</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>EXIT_ID</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>TIMING_ID</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>REVIEW_ID</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>缺口</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INFO-20260509-POWER-001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>SCORE, PLAN, EXIT, REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INFO-20260509-CRSR-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SCORE-20260509-CRSR-001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-CRSR-001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PLAN-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EXIT-1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TIME-1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GCTS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INFO-20260508-SCAN-001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>SCORE, PLAN, EXIT, REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INFO-20260509-MIST-001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EXIT-2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIME-2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>SCORE, REC/WATCH, PLAN, REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TRAW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INFO-20260508-SCAN-001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>SCORE, PLAN, EXIT, REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INFO-20260509-POWER-001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>✗(待)</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>SCORE, PLAN, EXIT, REVIEW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>欄位名稱</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>允許值</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>source_grade</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A1, A2, B, C, R, UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A1=官方公告 A2=主流媒體 B=研報 C=社群 R=傳聞</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>market_state</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>risk_on, selective_bull, neutral_range, risk_off, event_only</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>市場環境判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>momentum_state</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S0-A, S0-B, S0-C, S1, S2, S3, S4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>爆發動能狀態機</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>timing_state</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T0_clear, T1_caution, T2_restricted, T3_earnings_zone, T4_event_lockout, T5_post_event</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>時間閘門狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>final_grade</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A, B, C, D, F, P</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A=主推 B=可推 C=觀察 D=不推 F=禁止 P=待查</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>risk_lock</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pass, warning, blocked</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>風險封鎖狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rec_type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>primary, secondary, small_event, continuation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>推薦類型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>position_risk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>standard, half, small, forbidden</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>建議倉位水準</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>holding_action</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hold, add, reduce, stop_loss, wait</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>持倉動作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>next_action</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hold, add, reduce, exit, watch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>下一步建議</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>can_add</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>yes, no, conditional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>是否允許加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>exit_trigger</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>stop_loss, time_stop, t1_hit, t2_hit, trailing_stop, catalyst_fail, structure_break, manual</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>出場觸發類型</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>error_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>info_error, timing_error, chasing_error, sector_misjudge, risk_underestimate, catalyst_miss, market_turn, technical_fail, liquidity_misjudge, sec_dilution</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>復盤錯誤分類</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>review_period</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7d, 30d, 90d, 180d, 365d</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>復盤週期</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sector_grade</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A, B, C, WEAK</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A=85+ B=75-84 C=60-74 WEAK=&lt;60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>info_conclusion</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>adopt, observe, isolate, exclude</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>資訊處理結論</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>info_direction</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bullish, bearish, neutral, uncertain</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>初步方向判斷</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>concentration_verdict</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pass, warning, blocked</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>相關性集中度判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bias_verdict</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>clean, mild_bias, significant_bias, blocked</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>確認偏誤判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fatigue_verdict</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>clear, caution, restricted, blocked</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>決策疲勞判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sample_guard</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>insufficient(&lt;20), borderline(20-30), sufficient(30+)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>樣本量是否足夠做模型調整</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3891,8 +4801,49 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>SCORE-20260509-CRSR-001</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>CRSR</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-10T06:06:53.377153</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>HIGH_ALPHA_LAUNCHPAD_US_v2.1</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I2"/>
   <dataValidations count="2">
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：A,B,C,D,F,P" type="list">
       <formula1>"A,B,C,D,F,P"</formula1>
@@ -3911,7 +4862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3975,7 +4926,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>WATCH-20260509-004</t>
+          <t>WATCH-20260509-CRSR-001</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -3985,31 +4936,31 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>TRAW</t>
+          <t>CRSR</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>S1-A嚴格點火池</t>
+          <t>S1-B/S2交叉確認，PC/Gaming輪動初期，已進場持有</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>SEC/流動性/催化劑未查</t>
+          <t>板塊整體C級，IWM弱，尚未breakout 8.20</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>通過排雷後再評估</t>
+          <t>突破8.20+放量=升級為REC</t>
         </is>
       </c>
       <c r="H2" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
@@ -4020,7 +4971,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>WATCH-20260509-003</t>
+          <t>WATCH-20260509-004</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -4030,7 +4981,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>GCTS</t>
+          <t>TRAW</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -4065,7 +5016,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>WATCH-20260509-002</t>
+          <t>WATCH-20260509-003</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -4075,31 +5026,31 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>GCTS</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>AI power主線代表</t>
+          <t>S1-A嚴格點火池</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>位置可能偏高</t>
+          <t>SEC/流動性/催化劑未查</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>回踩確認</t>
+          <t>通過排雷後再評估</t>
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
@@ -4110,7 +5061,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>WATCH-20260509-001</t>
+          <t>WATCH-20260509-002</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -4120,7 +5071,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -4130,17 +5081,17 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>AI data center power主線，Goldman報告確認</t>
+          <t>AI power主線代表</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>需確認是否已大幅反映</t>
+          <t>位置可能偏高</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>回踩20EMA支撐+放量</t>
+          <t>回踩確認</t>
         </is>
       </c>
       <c r="H5" s="10" t="n">
@@ -4152,8 +5103,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>WATCH-20260509-001</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>AI data center power主線，Goldman報告確認</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>需確認是否已大幅反映</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>回踩20EMA支撐+放量</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I6"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入錯誤" error="請選擇有效值：core,standard,event,watch,pending,excluded" type="list">
       <formula1>"core,standard,event,watch,pending,excluded"</formula1>
